--- a/testdata/realdata/pon_ports.xlsx
+++ b/testdata/realdata/pon_ports.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>分光比</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -449,6 +454,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -466,6 +476,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -483,6 +498,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -500,6 +520,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -517,6 +542,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -534,6 +564,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -551,6 +586,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -568,6 +608,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -585,6 +630,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -602,6 +652,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -619,6 +674,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -636,6 +696,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -653,6 +718,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -670,6 +740,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -687,6 +762,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -704,6 +784,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -721,6 +806,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -738,6 +828,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -755,6 +850,11 @@
           <t>1:64</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -770,6 +870,11 @@
       <c r="C21" t="inlineStr">
         <is>
           <t>1:64</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>停用</t>
         </is>
       </c>
     </row>

--- a/testdata/realdata/pon_ports.xlsx
+++ b/testdata/realdata/pon_ports.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OLT-279116876</t>
+          <t>OLT-244077958</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OLT-279116876</t>
+          <t>OLT-244077958</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OLT-279116876</t>
+          <t>OLT-244077958</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OLT-279116876</t>
+          <t>OLT-244077958</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OLT-244077958</t>
+          <t>OLT-244081515</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OLT-244077958</t>
+          <t>OLT-244081515</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OLT-244077958</t>
+          <t>OLT-244081515</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OLT-244077958</t>
+          <t>OLT-244081515</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OLT-244081515</t>
+          <t>OLT-279116876</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OLT-244081515</t>
+          <t>OLT-279116876</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OLT-244081515</t>
+          <t>OLT-279116876</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OLT-244081515</t>
+          <t>OLT-279116876</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OLT-4059698545</t>
+          <t>OLT-304758391</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OLT-4059698545</t>
+          <t>OLT-304758391</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OLT-4059698545</t>
+          <t>OLT-304758391</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OLT-4059698545</t>
+          <t>OLT-304758391</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OLT-304758391</t>
+          <t>OLT-4059698545</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OLT-304758391</t>
+          <t>OLT-4059698545</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -837,7 +837,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OLT-304758391</t>
+          <t>OLT-4059698545</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OLT-304758391</t>
+          <t>OLT-4059698545</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
